--- a/q1_yichen/data_processing/2022Cdata_pre.xlsx
+++ b/q1_yichen/data_processing/2022Cdata_pre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yichenzhao/Desktop/工作/CUMCM-2022C-Practice/q1_yichen/data_processing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7F8627D-FE11-7A46-B58B-435EBE0D90E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC63935-7873-CF4E-B83F-A5BB905B1D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="1480" windowWidth="17100" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表单1_cleaning" sheetId="4" r:id="rId1"/>
@@ -18,12 +18,25 @@
     <sheet name="表单2" sheetId="2" r:id="rId3"/>
     <sheet name="表单3" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="176">
   <si>
     <t>表面风化</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1673,6 +1686,22 @@
   <si>
     <t>无风化</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>清洗颜色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风化编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>颜色缺失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1875,7 +1904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1944,6 +1973,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2747,16 +2782,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E83D3692-34B3-8541-8245-51CEE6E9165F}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="24" customWidth="1"/>
     <col min="2" max="5" width="10.6640625" style="6" customWidth="1"/>
     <col min="6" max="16384" width="8.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="19" customFormat="1" ht="14" customHeight="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:9" s="19" customFormat="1" ht="14" customHeight="1">
+      <c r="A1" s="23" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="18" t="s">
@@ -2771,8 +2806,20 @@
       <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15">
+      <c r="F1" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
       <c r="A2" s="7" t="s">
         <v>113</v>
       </c>
@@ -2788,8 +2835,24 @@
       <c r="E2" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15">
+      <c r="F2" s="6" t="str">
+        <f>IF(D2="","未知",TRIM(CLEAN(D2)))</f>
+        <v>蓝绿</v>
+      </c>
+      <c r="G2" s="6">
+        <f>IF(E2="风化",1,IF(E2="无风化",0,"检查"))</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <f>IF(D2="",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="str">
+        <f>IF(AND(A2&lt;&gt;"",OR(B2="A",B2="B",B2="C"),OR(C2="高钾",C2="铅钡"),OR(E2="风化",E2="无风化")),"通过","检查")</f>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
       <c r="A3" s="7" t="s">
         <v>115</v>
       </c>
@@ -2805,8 +2868,24 @@
       <c r="E3" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15">
+      <c r="F3" s="6" t="str">
+        <f t="shared" ref="F3:F59" si="0">IF(D3="","未知",TRIM(CLEAN(D3)))</f>
+        <v>浅蓝</v>
+      </c>
+      <c r="G3" s="6">
+        <f t="shared" ref="G3:G59" si="1">IF(E3="风化",1,IF(E3="无风化",0,"检查"))</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
+        <f t="shared" ref="H3:H66" si="2">IF(D3="",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <f t="shared" ref="I3:I66" si="3">IF(AND(A3&lt;&gt;"",OR(B3="A",B3="B",B3="C"),OR(C3="高钾",C3="铅钡"),OR(E3="风化",E3="无风化")),"通过","检查")</f>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
       <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
@@ -2822,8 +2901,24 @@
       <c r="E4" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+      <c r="F4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
@@ -2839,8 +2934,24 @@
       <c r="E5" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
+      <c r="F5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
       <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
@@ -2856,8 +2967,24 @@
       <c r="E6" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15">
+      <c r="F6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -2873,8 +3000,24 @@
       <c r="E7" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15">
+      <c r="F7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15">
       <c r="A8" s="7" t="s">
         <v>112</v>
       </c>
@@ -2890,8 +3033,24 @@
       <c r="E8" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="15">
+      <c r="F8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
       <c r="A9" s="7" t="s">
         <v>104</v>
       </c>
@@ -2907,8 +3066,24 @@
       <c r="E9" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="15">
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>紫</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
       <c r="A10" s="7" t="s">
         <v>33</v>
       </c>
@@ -2924,8 +3099,24 @@
       <c r="E10" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="15">
+      <c r="F10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
       <c r="A11" s="7" t="s">
         <v>34</v>
       </c>
@@ -2941,8 +3132,24 @@
       <c r="E11" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="15">
+      <c r="F11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
       <c r="A12" s="7" t="s">
         <v>116</v>
       </c>
@@ -2958,8 +3165,24 @@
       <c r="E12" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15">
+      <c r="F12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H12" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
       <c r="A13" s="7" t="s">
         <v>35</v>
       </c>
@@ -2975,8 +3198,24 @@
       <c r="E13" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="15">
+      <c r="F13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
       <c r="A14" s="7" t="s">
         <v>36</v>
       </c>
@@ -2992,8 +3231,24 @@
       <c r="E14" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="15">
+      <c r="F14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
       <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
@@ -3009,8 +3264,24 @@
       <c r="E15" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="15">
+      <c r="F15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深绿</v>
+      </c>
+      <c r="G15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15">
       <c r="A16" s="7" t="s">
         <v>38</v>
       </c>
@@ -3026,8 +3297,24 @@
       <c r="E16" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15">
+      <c r="F16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
       <c r="A17" s="7" t="s">
         <v>39</v>
       </c>
@@ -3043,8 +3330,24 @@
       <c r="E17" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="15">
+      <c r="F17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
       <c r="A18" s="7" t="s">
         <v>40</v>
       </c>
@@ -3060,8 +3363,24 @@
       <c r="E18" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="15">
+      <c r="F18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15">
       <c r="A19" s="7" t="s">
         <v>41</v>
       </c>
@@ -3077,8 +3396,24 @@
       <c r="E19" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="15">
+      <c r="F19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深蓝</v>
+      </c>
+      <c r="G19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
       <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
@@ -3092,8 +3427,24 @@
       <c r="E20" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="15">
+      <c r="F20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>未知</v>
+      </c>
+      <c r="G20" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15">
       <c r="A21" s="7" t="s">
         <v>43</v>
       </c>
@@ -3109,8 +3460,24 @@
       <c r="E21" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="15">
+      <c r="F21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15">
       <c r="A22" s="7" t="s">
         <v>114</v>
       </c>
@@ -3126,8 +3493,24 @@
       <c r="E22" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="15">
+      <c r="F22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15">
       <c r="A23" s="7" t="s">
         <v>117</v>
       </c>
@@ -3143,8 +3526,24 @@
       <c r="E23" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="15">
+      <c r="F23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15">
       <c r="A24" s="7" t="s">
         <v>119</v>
       </c>
@@ -3160,8 +3559,24 @@
       <c r="E24" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="15">
+      <c r="F24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G24" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15">
       <c r="A25" s="7" t="s">
         <v>44</v>
       </c>
@@ -3177,8 +3592,24 @@
       <c r="E25" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="15">
+      <c r="F25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>紫</v>
+      </c>
+      <c r="G25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15">
       <c r="A26" s="7" t="s">
         <v>45</v>
       </c>
@@ -3194,8 +3625,24 @@
       <c r="E26" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="15">
+      <c r="F26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H26" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15">
       <c r="A27" s="7" t="s">
         <v>46</v>
       </c>
@@ -3211,8 +3658,24 @@
       <c r="E27" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="15">
+      <c r="F27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>紫</v>
+      </c>
+      <c r="G27" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H27" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15">
       <c r="A28" s="7" t="s">
         <v>111</v>
       </c>
@@ -3228,8 +3691,24 @@
       <c r="E28" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15">
+      <c r="F28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15">
       <c r="A29" s="7" t="s">
         <v>47</v>
       </c>
@@ -3245,8 +3724,24 @@
       <c r="E29" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15">
+      <c r="F29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G29" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H29" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15">
       <c r="A30" s="7" t="s">
         <v>48</v>
       </c>
@@ -3262,8 +3757,24 @@
       <c r="E30" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="15">
+      <c r="F30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G30" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H30" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15">
       <c r="A31" s="7" t="s">
         <v>49</v>
       </c>
@@ -3279,8 +3790,24 @@
       <c r="E31" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15">
+      <c r="F31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深蓝</v>
+      </c>
+      <c r="G31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15">
       <c r="A32" s="7" t="s">
         <v>118</v>
       </c>
@@ -3296,8 +3823,24 @@
       <c r="E32" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="15">
+      <c r="F32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>紫</v>
+      </c>
+      <c r="G32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15">
       <c r="A33" s="7" t="s">
         <v>50</v>
       </c>
@@ -3313,8 +3856,24 @@
       <c r="E33" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="15">
+      <c r="F33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅绿</v>
+      </c>
+      <c r="G33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15">
       <c r="A34" s="7" t="s">
         <v>51</v>
       </c>
@@ -3330,8 +3889,24 @@
       <c r="E34" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="15">
+      <c r="F34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深绿</v>
+      </c>
+      <c r="G34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15">
       <c r="A35" s="7" t="s">
         <v>52</v>
       </c>
@@ -3347,8 +3922,24 @@
       <c r="E35" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="15">
+      <c r="F35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深绿</v>
+      </c>
+      <c r="G35" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15">
       <c r="A36" s="7" t="s">
         <v>53</v>
       </c>
@@ -3364,8 +3955,24 @@
       <c r="E36" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="15">
+      <c r="F36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅绿</v>
+      </c>
+      <c r="G36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15">
       <c r="A37" s="7" t="s">
         <v>54</v>
       </c>
@@ -3381,8 +3988,24 @@
       <c r="E37" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="15">
+      <c r="F37" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深绿</v>
+      </c>
+      <c r="G37" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H37" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15">
       <c r="A38" s="7" t="s">
         <v>55</v>
       </c>
@@ -3398,8 +4021,24 @@
       <c r="E38" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="15">
+      <c r="F38" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深绿</v>
+      </c>
+      <c r="G38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15">
       <c r="A39" s="7" t="s">
         <v>56</v>
       </c>
@@ -3415,8 +4054,24 @@
       <c r="E39" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="15">
+      <c r="F39" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深绿</v>
+      </c>
+      <c r="G39" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H39" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15">
       <c r="A40" s="7" t="s">
         <v>57</v>
       </c>
@@ -3432,8 +4087,24 @@
       <c r="E40" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="15">
+      <c r="F40" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>深绿</v>
+      </c>
+      <c r="G40" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H40" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15">
       <c r="A41" s="7" t="s">
         <v>58</v>
       </c>
@@ -3447,8 +4118,24 @@
       <c r="E41" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="15">
+      <c r="F41" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>未知</v>
+      </c>
+      <c r="G41" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H41" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I41" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15">
       <c r="A42" s="7" t="s">
         <v>59</v>
       </c>
@@ -3464,8 +4151,24 @@
       <c r="E42" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="15">
+      <c r="F42" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅绿</v>
+      </c>
+      <c r="G42" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H42" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15">
       <c r="A43" s="7" t="s">
         <v>60</v>
       </c>
@@ -3481,8 +4184,24 @@
       <c r="E43" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="15">
+      <c r="F43" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G43" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H43" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15">
       <c r="A44" s="7" t="s">
         <v>120</v>
       </c>
@@ -3498,8 +4217,24 @@
       <c r="E44" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="15">
+      <c r="F44" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G44" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15">
       <c r="A45" s="7" t="s">
         <v>61</v>
       </c>
@@ -3515,8 +4250,24 @@
       <c r="E45" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="15">
+      <c r="F45" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G45" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15">
       <c r="A46" s="7" t="s">
         <v>62</v>
       </c>
@@ -3532,8 +4283,24 @@
       <c r="E46" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="15">
+      <c r="F46" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15">
       <c r="A47" s="7" t="s">
         <v>63</v>
       </c>
@@ -3549,8 +4316,24 @@
       <c r="E47" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="15">
+      <c r="F47" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15">
       <c r="A48" s="7" t="s">
         <v>64</v>
       </c>
@@ -3566,8 +4349,24 @@
       <c r="E48" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" ht="15">
+      <c r="F48" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15">
       <c r="A49" s="7" t="s">
         <v>65</v>
       </c>
@@ -3581,8 +4380,24 @@
       <c r="E49" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="15">
+      <c r="F49" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>未知</v>
+      </c>
+      <c r="G49" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H49" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I49" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15">
       <c r="A50" s="7" t="s">
         <v>66</v>
       </c>
@@ -3598,8 +4413,24 @@
       <c r="E50" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="15">
+      <c r="F50" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>黑</v>
+      </c>
+      <c r="G50" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H50" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15">
       <c r="A51" s="7" t="s">
         <v>67</v>
       </c>
@@ -3615,8 +4446,24 @@
       <c r="E51" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="15">
+      <c r="F51" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>黑</v>
+      </c>
+      <c r="G51" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H51" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15">
       <c r="A52" s="7" t="s">
         <v>68</v>
       </c>
@@ -3632,8 +4479,24 @@
       <c r="E52" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="15">
+      <c r="F52" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G52" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H52" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15">
       <c r="A53" s="7" t="s">
         <v>69</v>
       </c>
@@ -3649,8 +4512,24 @@
       <c r="E53" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="15">
+      <c r="F53" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G53" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H53" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15">
       <c r="A54" s="7" t="s">
         <v>121</v>
       </c>
@@ -3666,8 +4545,24 @@
       <c r="E54" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="15">
+      <c r="F54" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G54" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H54" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15">
       <c r="A55" s="7" t="s">
         <v>70</v>
       </c>
@@ -3683,8 +4578,24 @@
       <c r="E55" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="15">
+      <c r="F55" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>浅蓝</v>
+      </c>
+      <c r="G55" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H55" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15">
       <c r="A56" s="7" t="s">
         <v>71</v>
       </c>
@@ -3700,8 +4611,24 @@
       <c r="E56" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="15">
+      <c r="F56" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>绿</v>
+      </c>
+      <c r="G56" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15">
       <c r="A57" s="7" t="s">
         <v>72</v>
       </c>
@@ -3717,8 +4644,24 @@
       <c r="E57" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="15">
+      <c r="F57" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G57" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15">
       <c r="A58" s="7" t="s">
         <v>73</v>
       </c>
@@ -3734,8 +4677,24 @@
       <c r="E58" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="15">
+      <c r="F58" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝绿</v>
+      </c>
+      <c r="G58" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H58" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15">
       <c r="A59" s="7" t="s">
         <v>74</v>
       </c>
@@ -3748,6 +4707,22 @@
       <c r="D59" s="3"/>
       <c r="E59" s="3" t="s">
         <v>122</v>
+      </c>
+      <c r="F59" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>未知</v>
+      </c>
+      <c r="G59" s="6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H59" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I59" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>通过</v>
       </c>
     </row>
   </sheetData>
